--- a/environment_data.xlsx
+++ b/environment_data.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Optimus\Desktop\MCM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E64125D-CF26-40F9-8CFF-01208D1D5172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A2E914-F11C-4A5A-A27A-D38075A16940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23596" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -47,6 +58,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -128,625 +140,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="7.9247594050743664E-2"/>
-          <c:y val="0.17222222222222225"/>
-          <c:w val="0.86486351706036746"/>
-          <c:h val="0.60984543598716823"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>CO2</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2024</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>398.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>400.2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>402.8</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>405.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>407.6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>410.3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>412.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>414.8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>417.2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>419.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-20C1-4081-BE95-3D3C45230AE8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="915441456"/>
-        <c:axId val="915448944"/>
-      </c:scatterChart>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PM2.5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2024</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$11</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>21.67</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>24.17</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>16.670000000000002</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>20.83</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>18.989999999999998</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.190000000000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>23.12</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>20.98</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-20C1-4081-BE95-3D3C45230AE8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="219245919"/>
-        <c:axId val="219227615"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="915441456"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="915448944"/>
-        <c:crossesAt val="395"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="915448944"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="in"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="915441456"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="219227615"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="in"/>
-        <c:minorTickMark val="in"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="219245919"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="219245919"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="219227615"/>
-        <c:crossesAt val="0"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
@@ -768,24 +161,24 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="tx2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="square"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln w="25400">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:schemeClr val="tx2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -798,34 +191,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -905,24 +298,26 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:symbol val="square"/>
+            <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="bg1">
+                  <a:alpha val="98000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln w="25400">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="accent6"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -935,34 +330,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
+                  <c:v>2014</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2015</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>2016</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>2017</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>2018</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>2019</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>2020</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>2021</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>2022</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1028,8 +423,8 @@
         <c:axId val="219259647"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="2025"/>
-          <c:min val="2014"/>
+          <c:max val="2024"/>
+          <c:min val="2013"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -1141,6 +536,7 @@
         <c:crossAx val="219256735"/>
         <c:crossesAt val="395"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="219256735"/>
@@ -1261,7 +657,7 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="219259647"/>
-        <c:crossesAt val="2014"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
@@ -1383,6 +779,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1531334943"/>
+        <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
@@ -1397,6 +794,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.32320450885668278"/>
+          <c:y val="2.2048611111111113E-2"/>
+          <c:w val="0.3535907809983897"/>
+          <c:h val="7.8456018518518522E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1435,9 +842,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1500,46 +905,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2056,572 +1421,20 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>135729</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>88106</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>569829</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>115106</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2421DE4-079F-4E76-90CE-243DCDABE5CC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>140493</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>11906</xdr:rowOff>
+      <xdr:colOff>188118</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>574593</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38906</xdr:rowOff>
+      <xdr:colOff>622218</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>41288</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2640,7 +1453,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2950,7 +1763,8 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>2015</v>
+        <f t="shared" ref="A2:A9" si="0">A3-1</f>
+        <v>2014</v>
       </c>
       <c r="B2">
         <v>21.67</v>
@@ -2961,7 +1775,8 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2016</v>
+        <f t="shared" si="0"/>
+        <v>2015</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -2972,7 +1787,8 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2017</v>
+        <f t="shared" si="0"/>
+        <v>2016</v>
       </c>
       <c r="B4">
         <v>24.17</v>
@@ -2983,7 +1799,8 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>2018</v>
+        <f t="shared" si="0"/>
+        <v>2017</v>
       </c>
       <c r="B5">
         <v>17.5</v>
@@ -2994,7 +1811,8 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>2019</v>
+        <f t="shared" si="0"/>
+        <v>2018</v>
       </c>
       <c r="B6">
         <v>16.670000000000002</v>
@@ -3005,7 +1823,8 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>2020</v>
+        <f t="shared" si="0"/>
+        <v>2019</v>
       </c>
       <c r="B7">
         <v>20.83</v>
@@ -3016,7 +1835,8 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>2021</v>
+        <f t="shared" si="0"/>
+        <v>2020</v>
       </c>
       <c r="B8">
         <v>18.989999999999998</v>
@@ -3027,7 +1847,8 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>2022</v>
+        <f t="shared" si="0"/>
+        <v>2021</v>
       </c>
       <c r="B9">
         <v>20.190000000000001</v>
@@ -3038,7 +1859,8 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>2023</v>
+        <f>A11-1</f>
+        <v>2022</v>
       </c>
       <c r="B10">
         <v>23.12</v>
@@ -3049,7 +1871,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B11">
         <v>20.98</v>
